--- a/datasets/Estaca 030/data_030.xlsx
+++ b/datasets/Estaca 030/data_030.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RYZEN5 2\Desktop\Datos modelo de descenso\Estaca 030\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RYZEN5 2\Desktop\scripts\DatabaseProyect\datasets\Estaca 030\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09308A3C-A100-4098-BF0F-AB22FBEF4B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A4A28A-FFE3-414A-8278-0347C658245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6660" yWindow="4470" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E2FE23EF-3BA0-4B1A-9FDA-27A148D0E338}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{E2FE23EF-3BA0-4B1A-9FDA-27A148D0E338}"/>
   </bookViews>
   <sheets>
     <sheet name="TZ0324052642" sheetId="1" r:id="rId1"/>
@@ -1008,36 +1008,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-MX"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -1415,6 +1385,316 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-4381-43C8-880D-426AF39D0580}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>data_030!$A$1:$A$44</c:f>
+              <c:strCache>
+                <c:ptCount val="44"/>
+                <c:pt idx="0">
+                  <c:v>time (min)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>data_030!$D$2:$D$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="43"/>
+                <c:pt idx="0">
+                  <c:v>27.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26.287178385666891</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.227278649339208</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.21778401282398</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.256297387038131</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22.340535680015815</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.46832437560688</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.637592369993325</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19.84636705376289</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.092769627861891</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18.375010642304844</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>17.691385747047349</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17.040271644932542</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16.420122237101083</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15.829464951711968</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15.26689724725637</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>14.731083282161622</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>14.220750742777089</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>13.734687822209844</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>13.271740342836324</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>12.830809015657156</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>12.410846829987458</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>12.010856567284245</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11.629888433207485</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>11.267037802291952</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>10.921443069874591</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>10.59228360617662</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>10.278777807682296</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.9801812411872568</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.6957848761093715</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9.4249134008646642</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>9.1669236193104986</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>8.9212029234482344</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>8.6871678387588123</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>8.4642626387170257</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8.2519580251946287</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>8.0497498716188325</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7.8571580259017306</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7.6737251702982316</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7.4990157354850933</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>7.332614866282551</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>7.1741274365625927</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>7.0231771110047045</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7F7E-42D5-99AB-6B082E34E475}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3914,11 +4194,11 @@
         <v>24.21778401282398</v>
       </c>
       <c r="E5" s="2">
-        <f t="shared" ref="E4:E44" si="3">(C5-D5)^2</f>
+        <f t="shared" ref="E5:E44" si="3">(C5-D5)^2</f>
         <v>6.1613962069922197</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
+        <f>ABS(C5-D5)</f>
         <v>2.4822159871760192</v>
       </c>
       <c r="H5">
@@ -3945,7 +4225,7 @@
         <v>23.256297387038131</v>
       </c>
       <c r="E6" s="2">
-        <f t="shared" si="3"/>
+        <f>(C6-D6)^2</f>
         <v>8.0866445509661684</v>
       </c>
       <c r="F6">
@@ -4315,7 +4595,7 @@
         <v>16.7</v>
       </c>
       <c r="D17">
-        <f t="shared" si="1"/>
+        <f>$S$4 + ($S$3-$S$4)*EXP(-$M$17*A17)</f>
         <v>15.26689724725637</v>
       </c>
       <c r="E17">
@@ -4323,7 +4603,7 @@
         <v>2.0537834999213671</v>
       </c>
       <c r="F17">
-        <f t="shared" si="0"/>
+        <f>ABS(C17-D17)</f>
         <v>1.4331027527436291</v>
       </c>
       <c r="H17">
@@ -4499,7 +4779,7 @@
         <v>13.4</v>
       </c>
       <c r="D22">
-        <f t="shared" si="1"/>
+        <f>$S$4 + ($S$3-$S$4)*EXP(-$M$17*A22)</f>
         <v>12.830809015657156</v>
       </c>
       <c r="E22">
@@ -5051,7 +5331,7 @@
         <v>1.6519580251946291</v>
       </c>
       <c r="H37">
-        <f t="shared" si="7"/>
+        <f>(1/(A37-A36))*(LN((C36-$S$4)/(C37-$S$4)))</f>
         <v>0.28620168728134687</v>
       </c>
       <c r="I37">
